--- a/registration_forms/026_public_service_award_night_rsvp_form--registration_forms.xlsx
+++ b/registration_forms/026_public_service_award_night_rsvp_form--registration_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -515,7 +515,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -543,18 +543,18 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>guest_count</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>Guest Count</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -566,12 +566,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>contact_email</t>
+          <t>guest_attendee_names</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>contact_email</t>
+          <t>Guest Attendee Names</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -589,12 +589,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>contact_phone</t>
+          <t>guest_attendee_email</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>contact_phone</t>
+          <t>Guest Attendee Email</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -607,23 +607,23 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>guest_count</t>
+          <t>will_attend</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>guest_count</t>
+          <t>Will Attend</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -635,12 +635,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>guest_attendee_names</t>
+          <t>comments</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>guest_attendee_names</t>
+          <t>Comments</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -658,12 +658,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>guest_attendee_email</t>
+          <t>special_requests</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>guest_attendee_email</t>
+          <t>Special Requests</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -676,63 +676,63 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>guest_attendee_phone</t>
+          <t>rsvp_type</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>guest_attendee_phone</t>
+          <t>RSVP Type</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>will_attend</t>
+          <t>guest_diet</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>will_attend</t>
+          <t>Guest Diet</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>time</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>comments</t>
+          <t>rsvp_time</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>comments</t>
+          <t>RSVP Time</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -745,17 +745,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>special_requests</t>
+          <t>rsvp_date</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>special_requests</t>
+          <t>RSVP Date</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -768,17 +768,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>rsvp_type</t>
+          <t>special_instructions</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>rsvp_type</t>
+          <t>Special Instructions</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -791,299 +791,23 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>guest_diet</t>
+          <t>confirm_attendance</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>guest_diet</t>
+          <t>Confirm Attendance</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>guest_diet_notes</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>guest_diet_notes</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>rsvp_time</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>rsvp_time</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>rsvp_date</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>rsvp_date</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>special_instructions</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>special_instructions</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>rsvp_type</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>rsvp_type</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>rsvp_type_details</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>rsvp_type_details</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>comments</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>comments</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>confirm_attendance</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>confirm_attendance</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>rsvp_type</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>rsvp_type</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>rsvp_type_details</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>rsvp_type_details</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>rsvp_type</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>rsvp_type</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>special_instructions</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>special_instructions</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -1098,12 +822,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C19"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1165,12 +889,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'name':_'rsvp',_'description':_none,_'value':_'rsvp'}</t>
+          <t>in_person</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'name': 'RSVP', 'description': None, 'value': 'RSVP'}</t>
+          <t>In Person</t>
         </is>
       </c>
     </row>
@@ -1182,12 +906,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'name':_'not_rsvp',_'description':_none,_'value':_'not_rsvp'}</t>
+          <t>virtual</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'name': 'Not RSVP', 'description': None, 'value': 'Not RSVP'}</t>
+          <t>Virtual</t>
         </is>
       </c>
     </row>
@@ -1199,12 +923,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'name':_'vegan',_'description':_'vegan',_'value':_'vegan'}</t>
+          <t>vegan</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'name': 'Vegan', 'description': 'Vegan', 'value': 'Vegan'}</t>
+          <t>Vegan</t>
         </is>
       </c>
     </row>
@@ -1216,12 +940,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'name':_'vegetarian',_'description':_none,_'value':_'vegetarian'}</t>
+          <t>vegetarian</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'name': 'Vegetarian', 'description': None, 'value': 'Vegetarian'}</t>
+          <t>Vegetarian</t>
         </is>
       </c>
     </row>
@@ -1233,12 +957,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'name':_'omnivore',_'description':_none,_'value':_'omnivore'}</t>
+          <t>omnivore</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'name': 'Omnivore', 'description': None, 'value': 'Omnivore'}</t>
+          <t>Omnivore</t>
         </is>
       </c>
     </row>
@@ -1250,182 +974,46 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'name':_'none',_'description':_none,_'value':_'none'}</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'name': 'None', 'description': None, 'value': 'None'}</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>rsvp_type_choices</t>
+          <t>confirm_attendance_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'name':_'in_person',_'description':_none,_'value':_'in_person'}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'name': 'In Person', 'description': None, 'value': 'In Person'}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>rsvp_type_choices</t>
+          <t>confirm_attendance_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'name':_'virtual',_'description':_none,_'value':_'virtual'}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'name': 'Virtual', 'description': None, 'value': 'Virtual'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>rsvp_type_choices</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>{'name':_'phone_call',_'description':_none,_'value':_'phone_call'}</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>{'name': 'Phone Call', 'description': None, 'value': 'Phone Call'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>confirm_attendance_choices</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>{'name':_true,_'description':_none,_'value':_true}</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>{'name': True, 'description': None, 'value': True}</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>confirm_attendance_choices</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>{'name':_false,_'description':_none,_'value':_false}</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>{'name': False, 'description': None, 'value': False}</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>rsvp_type_choices</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>{'name':_'in_person',_'description':_none,_'value':_'in_person'}</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>{'name': 'In Person', 'description': None, 'value': 'In Person'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>rsvp_type_choices</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>{'name':_'virtual',_'description':_none,_'value':_'virtual'}</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>{'name': 'Virtual', 'description': None, 'value': 'Virtual'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>rsvp_type_choices</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>{'name':_'phone_call',_'description':_none,_'value':_'phone_call'}</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>{'name': 'Phone Call', 'description': None, 'value': 'Phone Call'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>rsvp_type_choices</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>{'name':_'rsvp',_'description':_none,_'value':_'rsvp'}</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>{'name': 'RSVP', 'description': None, 'value': 'RSVP'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>rsvp_type_choices</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>{'name':_'not_rsvp',_'description':_none,_'value':_'not_rsvp'}</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>{'name': 'Not RSVP', 'description': None, 'value': 'Not RSVP'}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
